--- a/tame_output/ON/bt/strategyON_20240310.xlsx
+++ b/tame_output/ON/bt/strategyON_20240310.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-193.5%</t>
+          <t>-193.8%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-106.3%</t>
+          <t>-106.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-59.0%</t>
+          <t>-59.2%</t>
         </is>
       </c>
     </row>
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.3191947158878455</v>
+        <v>-0.3224784086730598</v>
       </c>
       <c r="E1898" t="n">
-        <v>3.036235833047008</v>
+        <v>3.034922355932923</v>
       </c>
       <c r="F1898" t="n">
-        <v>1.177042670551735</v>
+        <v>1.173758977766521</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.870495746046935</v>
+        <v>3.868525530375807</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240310.xlsx
+++ b/tame_output/ON/bt/strategyON_20240310.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-193.8%</t>
+          <t>-193.9%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.8%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-106.6%</t>
+          <t>-106.7%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.41569499518759</v>
+        <v>3.415694995187589</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.3224784086730598</v>
+        <v>-0.3232414148820838</v>
       </c>
       <c r="E1898" t="n">
-        <v>3.034922355932923</v>
+        <v>3.034617153449313</v>
       </c>
       <c r="F1898" t="n">
-        <v>1.173758977766521</v>
+        <v>1.172995971557497</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.868525530375807</v>
+        <v>3.868067726650393</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240310.xlsx
+++ b/tame_output/ON/bt/strategyON_20240310.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-35.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>468.1%</t>
+          <t>466.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-193.9%</t>
+          <t>-221.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-83.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-106.7%</t>
+          <t>-134.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-59.2%</t>
+          <t>-76.0%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.415694995187589</v>
+        <v>3.41569499518759</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.3232414148820838</v>
+        <v>-0.6021727344781167</v>
       </c>
       <c r="E1898" t="n">
-        <v>3.034617153449313</v>
+        <v>2.9230446256109</v>
       </c>
       <c r="F1898" t="n">
-        <v>1.172995971557497</v>
+        <v>0.8940646519614643</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.868067726650393</v>
+        <v>3.700708934892773</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240310.xlsx
+++ b/tame_output/ON/bt/strategyON_20240310.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>-26.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,52 +1456,52 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-161.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1898"/>
+  <dimension ref="A1:G1899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.41569499518759</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45215,6 +45215,29 @@
       </c>
       <c r="G1898" t="n">
         <v>3.700708934892773</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="2" t="n">
+        <v>45361</v>
+      </c>
+      <c r="B1899" t="n">
+        <v>3.421814075753193</v>
+      </c>
+      <c r="C1899" t="n">
+        <v>2.847839677117512</v>
+      </c>
+      <c r="D1899" t="n">
+        <v>-0.6021727344781167</v>
+      </c>
+      <c r="E1899" t="n">
+        <v>2.9230446256109</v>
+      </c>
+      <c r="F1899" t="n">
+        <v>0.8940646519614643</v>
+      </c>
+      <c r="G1899" t="n">
+        <v>2.84090347410388</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240310.xlsx
+++ b/tame_output/ON/bt/strategyON_20240310.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-35.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-206.8%</t>
+          <t>-206.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-81.3%</t>
+          <t>-81.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.6%</t>
         </is>
       </c>
     </row>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-3.984342941507316</v>
+        <v>-3.974183944360967</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.524785092776015</v>
+        <v>1.528848691634555</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.2366917757797393</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-3.998057805832428</v>
+        <v>-3.987898808686078</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.515398712191665</v>
+        <v>1.519462311050205</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.2366917757797393</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-4.003574725676394</v>
+        <v>-3.993415728530045</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.51159686430908</v>
+        <v>1.515660463167619</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.2366917757797393</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-4.00838776414173</v>
+        <v>-3.998228766995382</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.513450624852153</v>
+        <v>1.517514223710693</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.2382384104825251</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-4.006270605417438</v>
+        <v>-3.996111608271089</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.510271183807467</v>
+        <v>1.514334782666007</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.2382384104825251</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-4.005793258838947</v>
+        <v>-3.995634261692599</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.510360021117279</v>
+        <v>1.514423619975819</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.2382384104825251</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-4.00476847253209</v>
+        <v>-3.994609475385741</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.513341451611452</v>
+        <v>1.517405050469992</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.2372136241756675</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-4.023509852791008</v>
+        <v>-4.01335085564466</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.511195202805935</v>
+        <v>1.515258801664475</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.2372136241756675</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-4.036479195576107</v>
+        <v>-4.026320198429758</v>
       </c>
       <c r="E1875" t="n">
-        <v>1.513923485649073</v>
+        <v>1.517987084507613</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.2501829669607661</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-4.030003048782548</v>
+        <v>-4.019844051636198</v>
       </c>
       <c r="E1876" t="n">
-        <v>1.519555694988266</v>
+        <v>1.523619293846806</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.2437068201672065</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-4.026312123826136</v>
+        <v>-4.016153126679787</v>
       </c>
       <c r="E1877" t="n">
-        <v>1.52103206497083</v>
+        <v>1.52509566382937</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.2437068201672065</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-4.01909677095432</v>
+        <v>-4.008937773807971</v>
       </c>
       <c r="E1878" t="n">
-        <v>1.529431403238199</v>
+        <v>1.533495002096739</v>
       </c>
       <c r="F1878" t="n">
         <v>-0.1739285848768247</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-3.968068924872494</v>
+        <v>-3.957909927726145</v>
       </c>
       <c r="E1879" t="n">
-        <v>1.554325096155365</v>
+        <v>1.558388695013905</v>
       </c>
       <c r="F1879" t="n">
         <v>-0.0987192465697237</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-3.894599093205046</v>
+        <v>-3.884440096058697</v>
       </c>
       <c r="E1880" t="n">
-        <v>1.599084730315766</v>
+        <v>1.603148329174306</v>
       </c>
       <c r="F1880" t="n">
         <v>-0.02524941490227528</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-3.814226737741116</v>
+        <v>-3.804067740594767</v>
       </c>
       <c r="E1881" t="n">
-        <v>1.645788893248855</v>
+        <v>1.649852492107395</v>
       </c>
       <c r="F1881" t="n">
         <v>0.05512294056165434</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-3.781294867928266</v>
+        <v>-3.771135870781916</v>
       </c>
       <c r="E1882" t="n">
-        <v>1.651742476272399</v>
+        <v>1.655806075130939</v>
       </c>
       <c r="F1882" t="n">
         <v>0.05512294056165434</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-3.801459509477813</v>
+        <v>-3.791300512331464</v>
       </c>
       <c r="E1883" t="n">
-        <v>1.637004428878604</v>
+        <v>1.641068027737144</v>
       </c>
       <c r="F1883" t="n">
         <v>0.03495829901210701</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-3.74279257945628</v>
+        <v>-3.732633582309931</v>
       </c>
       <c r="E1884" t="n">
-        <v>1.661586990725773</v>
+        <v>1.665650589584313</v>
       </c>
       <c r="F1884" t="n">
         <v>0.1199177674422447</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-3.67972334714994</v>
+        <v>-3.669564350003591</v>
       </c>
       <c r="E1885" t="n">
-        <v>1.689508412277424</v>
+        <v>1.693572011135964</v>
       </c>
       <c r="F1885" t="n">
         <v>0.09140420476001021</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-3.627707833181128</v>
+        <v>-3.617548836034779</v>
       </c>
       <c r="E1886" t="n">
-        <v>1.71430495355135</v>
+        <v>1.71836855240989</v>
       </c>
       <c r="F1886" t="n">
         <v>0.09140420476001021</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-3.452138164260224</v>
+        <v>-3.441979167113875</v>
       </c>
       <c r="E1887" t="n">
-        <v>1.78305759422097</v>
+        <v>1.78712119307951</v>
       </c>
       <c r="F1887" t="n">
         <v>0.09140420476001021</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-3.254868758532226</v>
+        <v>-3.244709761385876</v>
       </c>
       <c r="E1888" t="n">
-        <v>1.877018766677041</v>
+        <v>1.881082365535581</v>
       </c>
       <c r="F1888" t="n">
         <v>0.2886736104880083</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-3.055716651295127</v>
+        <v>-3.045557654148777</v>
       </c>
       <c r="E1889" t="n">
-        <v>1.943628475925198</v>
+        <v>1.947692074783738</v>
       </c>
       <c r="F1889" t="n">
         <v>0.4539961364378217</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-2.829871498575716</v>
+        <v>-2.819712501429366</v>
       </c>
       <c r="E1890" t="n">
-        <v>2.043545610049171</v>
+        <v>2.047609208907711</v>
       </c>
       <c r="F1890" t="n">
         <v>0.4959228120249853</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-2.543596686253021</v>
+        <v>-2.533437689106672</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.159194679534307</v>
+        <v>2.163258278392847</v>
       </c>
       <c r="F1891" t="n">
         <v>0.4959228120249853</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-2.316800859179688</v>
+        <v>-2.306641862033338</v>
       </c>
       <c r="E1892" t="n">
-        <v>2.252546784525749</v>
+        <v>2.256610383384289</v>
       </c>
       <c r="F1892" t="n">
         <v>0.5640367566465299</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-2.032892128250939</v>
+        <v>-2.02273313110459</v>
       </c>
       <c r="E1893" t="n">
-        <v>2.371843981135885</v>
+        <v>2.375907579994425</v>
       </c>
       <c r="F1893" t="n">
         <v>0.5640367566465299</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-1.785904878057987</v>
+        <v>-1.775745880911638</v>
       </c>
       <c r="E1894" t="n">
-        <v>2.4609016188192</v>
+        <v>2.46496521767774</v>
       </c>
       <c r="F1894" t="n">
         <v>0.8110240068394819</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-1.522068010853918</v>
+        <v>-1.511909013707569</v>
       </c>
       <c r="E1895" t="n">
-        <v>2.55655288438792</v>
+        <v>2.56061648324646</v>
       </c>
       <c r="F1895" t="n">
         <v>0.8110240068394819</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-1.254826209985521</v>
+        <v>-1.244667212839172</v>
       </c>
       <c r="E1896" t="n">
-        <v>2.661615044235905</v>
+        <v>2.665678643094445</v>
       </c>
       <c r="F1896" t="n">
         <v>0.8110240068394819</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-0.9790170465850366</v>
+        <v>-0.9688580494386875</v>
       </c>
       <c r="E1897" t="n">
-        <v>2.771638394622638</v>
+        <v>2.775701993481178</v>
       </c>
       <c r="F1897" t="n">
         <v>0.9000433151182154</v>
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.705298952527836</v>
+        <v>-0.6997904616717081</v>
       </c>
       <c r="E1898" t="n">
-        <v>2.881794138391012</v>
+        <v>2.883997534733464</v>
       </c>
       <c r="F1898" t="n">
-        <v>1.173761409175416</v>
+        <v>1.169110902885195</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.868526989221144</v>
+        <v>3.865736685447011</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.439833833167122</v>
+        <v>3.439833833167123</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-0.4522999981420953</v>
+        <v>-0.4473638277216077</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.969733403983556</v>
+        <v>2.971707872151752</v>
       </c>
       <c r="F1899" t="n">
-        <v>1.426760363561157</v>
+        <v>1.421537536835295</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.007066045690836</v>
+        <v>4.00393234965532</v>
       </c>
     </row>
   </sheetData>
